--- a/Models/Яйца/results/Яйца - Лучшие модели.xlsx
+++ b/Models/Яйца/results/Яйца - Лучшие модели.xlsx
@@ -462,13 +462,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.27</v>
+        <v>4.42</v>
       </c>
       <c r="C2" t="n">
-        <v>6.72</v>
+        <v>4.77</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>4.45</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -483,13 +483,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.93</v>
+        <v>6.64</v>
       </c>
       <c r="C3" t="n">
-        <v>6.2</v>
+        <v>7.65</v>
       </c>
       <c r="D3" t="n">
-        <v>7.95</v>
+        <v>12.02</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -504,17 +504,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.25</v>
+        <v>9.16</v>
       </c>
       <c r="C4" t="n">
-        <v>11.34</v>
+        <v>8.23</v>
       </c>
       <c r="D4" t="n">
-        <v>16.39</v>
+        <v>13.93</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.92</v>
+        <v>12.95</v>
       </c>
       <c r="C5" t="n">
-        <v>60.52</v>
+        <v>19.69</v>
       </c>
       <c r="D5" t="n">
-        <v>82.17</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -546,17 +546,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.91</v>
+        <v>8.49</v>
       </c>
       <c r="C6" t="n">
-        <v>6.32</v>
+        <v>8.02</v>
       </c>
       <c r="D6" t="n">
-        <v>20.98</v>
+        <v>11.21</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.22</v>
+        <v>11.53</v>
       </c>
       <c r="C7" t="n">
-        <v>16.11</v>
+        <v>6.3</v>
       </c>
       <c r="D7" t="n">
         <v>38.15</v>
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>144.4</v>
+        <v>138.61</v>
       </c>
       <c r="C8" t="n">
-        <v>89.75</v>
+        <v>104.96</v>
       </c>
       <c r="D8" t="n">
-        <v>75.83</v>
+        <v>72.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -609,17 +609,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.94</v>
+        <v>9.08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.99</v>
+        <v>13.82</v>
       </c>
       <c r="D9" t="n">
-        <v>5.36</v>
+        <v>9.49</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -630,17 +630,17 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.52</v>
+        <v>13.57</v>
       </c>
       <c r="C10" t="n">
-        <v>18.91</v>
+        <v>20.33</v>
       </c>
       <c r="D10" t="n">
-        <v>13.42</v>
+        <v>24.05</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -651,17 +651,17 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.87</v>
+        <v>7.66</v>
       </c>
       <c r="C11" t="n">
-        <v>6.9</v>
+        <v>6.94</v>
       </c>
       <c r="D11" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.94</v>
+        <v>6.58</v>
       </c>
       <c r="C12" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="D12" t="n">
-        <v>9.550000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -693,17 +693,17 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20.65</v>
+        <v>17.75</v>
       </c>
       <c r="C13" t="n">
-        <v>19.18</v>
+        <v>15.54</v>
       </c>
       <c r="D13" t="n">
-        <v>16.75</v>
+        <v>20.41</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.210000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>6.51</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>5.42</v>
+        <v>11.83</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.18</v>
+        <v>19.85</v>
       </c>
       <c r="C15" t="n">
-        <v>8.42</v>
+        <v>3.98</v>
       </c>
       <c r="D15" t="n">
-        <v>48.11</v>
+        <v>40.19</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -756,13 +756,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.41</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>12.75</v>
+        <v>11.98</v>
       </c>
       <c r="D16" t="n">
-        <v>40.08</v>
+        <v>21.98</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7.53</v>
+        <v>5.67</v>
       </c>
       <c r="C17" t="n">
-        <v>9.390000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="D17" t="n">
-        <v>13.71</v>
+        <v>19.13</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -798,17 +798,17 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23.75</v>
+        <v>29.4</v>
       </c>
       <c r="C18" t="n">
-        <v>20.19</v>
+        <v>37.34</v>
       </c>
       <c r="D18" t="n">
-        <v>46.92</v>
+        <v>49.84</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -819,17 +819,17 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.42</v>
+        <v>4.85</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>5.28</v>
       </c>
       <c r="D19" t="n">
-        <v>6.29</v>
+        <v>6.07</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16.53</v>
+        <v>10.79</v>
       </c>
       <c r="C20" t="n">
-        <v>12.68</v>
+        <v>6.15</v>
       </c>
       <c r="D20" t="n">
-        <v>16.81</v>
+        <v>15.48</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -861,17 +861,17 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.98</v>
+        <v>7.09</v>
       </c>
       <c r="C21" t="n">
-        <v>10.77</v>
+        <v>6.22</v>
       </c>
       <c r="D21" t="n">
-        <v>9.27</v>
+        <v>10.14</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
